--- a/data/suppliers/rati-products.xlsx
+++ b/data/suppliers/rati-products.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="SheetName"/>
   </sheets>
   <definedNames>
-    <definedName name="SheetName">SheetName!$A$1:$B$148</definedName>
+    <definedName name="SheetName">SheetName!$A$1:$B$152</definedName>
   </definedNames>
   <calcPr calcId="122211" fullCalcOnLoad="true"/>
 </workbook>
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -358,886 +358,936 @@
     <row outlineLevel="0" r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>ARM3-04</t>
+          <t>ARM3-01</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C4 след 2021 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C3 2009-2016</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>ARM3-12</t>
+          <t>ARM3-02</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat Tipo след 2016 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C3 след 2017 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>ARM3-20</t>
+          <t>ARM3-03</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Astra H 2004-2013</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C4 Cactus 2014-2021</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>ARM3-03</t>
+          <t>ARM3-04</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C4 Cactus 2014-2021</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C4 след 2021 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>ARM3-11</t>
+          <t>ARM3-05</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500e след 2020 година, само за електрическата версия</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Dokker след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>ARM3-19</t>
+          <t>ARM3-06</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Honda Jazz 2016-2019</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Duster 2009-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>ARM3-27</t>
+          <t>ARM3-07</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira B 2005-2007</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Duster след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>ARM3-35</t>
+          <t>ARM3-08</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Polo 2009-2017</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Spring след 2021 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>ARMS-05</t>
+          <t>ARM3-09</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Dokker след 2018 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500 2008-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>ARM3-28</t>
+          <t>ARM3-10</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira B 2007-2014</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500 след 2016 година, без електрическата версия</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>ARM3-36</t>
+          <t>ARM3-11</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Polo след 2018 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500e след 2020 година, само за електрическата версия</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>ARMS-06</t>
+          <t>ARM3-12</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Duster 2009-2017</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat Tipo след 2016 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>ARMS-14</t>
+          <t>ARM3-13</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Ford Focus 2004-2012</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Fiesta след 2017 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>ARMS-22</t>
+          <t>ARM3-14</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Opel Astra K след 2015 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Ford Focus 2004-2012</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>ARMS-30</t>
+          <t>ARM3-15</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Renault Clio 2013-2019</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus 2011-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>ARMS-13</t>
+          <t>ARM3-16</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Fiesta след 2017 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus 2015-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>ARMS-21</t>
+          <t>ARM3-17</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra J 2009-2015</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>ARMS-29</t>
+          <t>ARM3-18</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira C Tourer 2011-2019</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Honda Jazz 2008-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>ARM3-01</t>
+          <t>ARM3-19</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C3 2009-2016</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Honda Jazz 2016-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>ARM3-09</t>
+          <t>ARM3-20</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500 2008-2015</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Astra H 2004-2013</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>ARM3-17</t>
+          <t>ARM3-21</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus след 2018 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Astra J 2009-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>ARM3-06</t>
+          <t>ARM3-22</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Duster 2009-2017</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Opel Astra K след 2015 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>ARM3-14</t>
+          <t>ARM3-23</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Ford Focus 2004-2012</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa D 2006-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>ARM3-22</t>
+          <t>ARM3-24</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Opel Astra K след 2015 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa E 2014-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>ARM3-02</t>
+          <t>ARM3-25</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Citroen C3 след 2017 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa F след 2020 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>ARM3-10</t>
+          <t>ARM3-26</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Fiat 500 след 2016 година, без електрическата версия</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Meriva 2010-2017 без подвижда релса в средната конзола</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>ARM3-18</t>
+          <t>ARM3-27</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Honda Jazz 2008-2015</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira B 2005-2007</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>ARM3-25</t>
+          <t>ARM3-28</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa F след 2020 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira B 2007-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>ARM3-33</t>
+          <t>ARM3-29</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Golf 5 2003-2010</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira C Tourer 2011-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>ARMS-03</t>
+          <t>ARM3-30</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 Cactus 2014-2021</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Renault Clio 2013-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>ARM3-26</t>
+          <t>ARM3-31</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Meriva 2010-2017 без подвижда релса в средната конзола</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Caddy 2004-2020</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>ARM3-34</t>
+          <t>ARM3-32</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Golf 7 2012-2019</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Caddy след 2020 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>ARMS-04</t>
+          <t>ARM3-33</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 след 2021 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Golf 5 2003-2010</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>ARM3-07</t>
+          <t>ARM3-34</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Duster след 2018 година</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Golf 7 2012-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>ARM3-15</t>
+          <t>ARM3-35</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus 2011-2014</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Polo 2009-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>ARM3-23</t>
+          <t>ARM3-36</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa D 2006-2014</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Polo след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>ARMS-11</t>
+          <t>ARM3-37</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500e след 2020 година, само за електрическата версия</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Touran 2003-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>ARMS-19</t>
+          <t>ARM3-38</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Honda Jazz 2016-2019</t>
+          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Ford Fiesta 2008-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>ARMS-27</t>
+          <t>ARMS-01</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira B 2005-2007</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C3 2009-2016, DS3 2010-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>ARMS-12</t>
+          <t>ARMS-02</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat Tipo след 2016 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C3 след 2017 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>ARMS-20</t>
+          <t>ARMS-03</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra H 2004-2013</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 Cactus 2014-2021</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>ARMS-28</t>
+          <t>ARMS-04</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira B 2007-2014</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 след 2021 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>ARM3-05</t>
+          <t>ARMS-05</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Dokker след 2018 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Dokker след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>ARM3-13</t>
+          <t>ARMS-06</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Fiesta след 2017 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Duster 2009-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>ARM3-21</t>
+          <t>ARMS-07</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Astra J 2009-2015</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Duster след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>ARM3-08</t>
+          <t>ARMS-08</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Dacia Spring след 2021 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Spring след 2021 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>ARM3-16</t>
+          <t>ARMS-09</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа, USB и AUX за Ford Focus 2015-2017</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500 2008-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>ARM3-24</t>
+          <t>ARMS-10</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Corsa E 2014-2019</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500 след 2016 година, без електрическата версия</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>ARM3-29</t>
+          <t>ARMS-11</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Opel Zafira C Tourer 2011-2019</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500e след 2020 година, само за електрическата версия</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>ARM3-37</t>
+          <t>ARMS-12</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Touran 2003-2015</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat Tipo след 2016 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>V00796AW</t>
+          <t>ARMS-13</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C1, Peugeot 108, Toyota Aygo след 2014 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Fiesta след 2017 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>ARMS-36</t>
+          <t>ARMS-14</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo след 2018 година</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Ford Focus 2004-2012</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>V00614BW</t>
+          <t>ARMS-15</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot Bipper 2008-2015</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus 2011-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>V00903W</t>
+          <t>ARMS-16</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Skoda Octavia 1997-2009</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus 2015-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>ARMS-37</t>
+          <t>ARMS-17</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Touran 2003-2015</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>V00631W</t>
+          <t>ARMS-18</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за KIA Ceed 2006-2012</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Honda Jazz 2008-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>V01070AW</t>
+          <t>ARMS-19</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Dacia Dokker, Lodgy след 2015 година, Dacia Logan, Sandero след 2017 година с фабричен подлакътник</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Honda Jazz 2016-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>ARM3-31</t>
+          <t>ARMS-20</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Caddy 2004-2020</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra H 2004-2013</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>ARMS-01</t>
+          <t>ARMS-21</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C3 2009-2016, DS3 2010-2019</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra J 2009-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>V00602W</t>
+          <t>ARMS-22</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 2004-2011</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Opel Astra K след 2015 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>V01344</t>
+          <t>ARMS-23</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива със зелено сива дръжка</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa D 2006-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>V01575A</t>
+          <t>ARMS-24</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa E 2014-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>V01600</t>
+          <t>ARMS-25</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa F след 2020 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>V01625</t>
+          <t>ARMS-26</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Meriva 2010-2017 без подвижда релса в средната конзола</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>ARM3-30</t>
+          <t>ARMS-27</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Renault Clio 2013-2019</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira B 2005-2007</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>ARM3-38</t>
+          <t>ARMS-28</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Ford Fiesta 2008-2017</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira B 2007-2014</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>V00865</t>
+          <t>ARMS-29</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot 307 2001-2008</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Zafira C Tourer 2011-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>V01350</t>
+          <t>ARMS-30</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>ЗАКАЧАЛКА RATI С АДАПТЕР ЗА СЕДАЛКА</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Renault Clio 2013-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>V01573</t>
+          <t>ARMS-31</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Caddy 2004-2020</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>V01585</t>
+          <t>ARMS-32</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Caddy след 2020 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>V01618</t>
+          <t>ARMS-33</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Golf 5 2003-2010</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>V01647</t>
+          <t>ARMS-34</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Golf 7 2012-2019</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>V01792</t>
+          <t>ARMS-35</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>Кутия Rati Frunk за преден багажник на Fiat 500e след 2020 година 13L, 44x31x6/13cm, черна</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo 2009-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>V00866</t>
+          <t>ARMS-36</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Meriva 2003-2009</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>V01561</t>
+          <t>ARMS-37</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Touran 2003-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>V01579</t>
+          <t>ARMS-38</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Ford Fiesta 2008-2017</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>V01603</t>
+          <t>V00602W</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C4 2004-2011</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>ARMS-35</t>
+          <t>V00604</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo 2009-2017</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo 2001-2009</t>
         </is>
       </c>
     </row>
@@ -1256,577 +1306,532 @@
     <row outlineLevel="0" r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>V00902W</t>
+          <t>V00614BW</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat Doblo 2015-2022</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot Bipper 2008-2015</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>V01574A</t>
+          <t>V00631W</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за KIA Ceed 2006-2012</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>V01586</t>
+          <t>V00741W</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra G 1998-2009</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t>V01620</t>
+          <t>V00796AW</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C1, Peugeot 108, Toyota Aygo след 2014 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>V01651</t>
+          <t>V00865</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot 307 2001-2008</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>V01768</t>
+          <t>V00866</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>ЧАНТА RATI ЗА СЕДАЛКА НА АВТОМОБИЛ 38X48CM</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Meriva 2003-2009</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>V01659</t>
+          <t>V00867</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot 206 1998-2012</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>V01771</t>
+          <t>V00902W</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>КОМПЛЕКТ ЗЕЛЕНИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat Doblo 2015-2022</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t>V01802A</t>
+          <t>V00903W</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Ford Transit след 2013 година за модела с фабричен подлакътник</t>
+          <t>Подлакътник Rati модел Armster S с черна еко кожа за Skoda Octavia 1997-2009</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>V01737</t>
+          <t>V01070AW</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Dacia Dokker, Lodgy след 2015 година, Dacia Logan, Sandero след 2017 година с фабричен подлакътник</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t>V01578</t>
+          <t>V01085W</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Ford Transit Connect след 2018 година</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t>V01601</t>
+          <t>V01344</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива със зелено сива дръжка</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>V01633</t>
+          <t>V01350</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>ЗАКАЧАЛКА RATI С АДАПТЕР ЗА СЕДАЛКА</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t>V01667</t>
+          <t>V01561</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>V01743</t>
+          <t>V01566</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t>V01634</t>
+          <t>V01571</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t>V01782A</t>
-        </is>
-      </c>
-      <c r="B97" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Fiat Ducato, Peugeot Boxer, Citroen Jumper след 2006 година, Opel Movano след 2021 година, Ram Promaster след 2014 година за моделите с фабричен подлакътник</t>
+          <t>V01573</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>V01669</t>
+          <t>V01574A</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>V01762</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива със синьо сива дръжка</t>
+          <t>V01574B</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>V01683</t>
+          <t>V01575A</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>V01571</t>
+          <t>V01578</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>V01584</t>
+          <t>V01579</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>V01613</t>
+          <t>V01580</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>V01640</t>
+          <t>V01584</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>V01790A</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Volkswagen T5 2003-2016, T6 2016-2022, T7 след 2022 година, ID.Buzz след 2022 година за моделите с фабричен подлакътник</t>
+          <t>V01585</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>ARMS-38</t>
-        </is>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Ford Fiesta 2008-2017</t>
+          <t>V01586</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>V00741W</t>
-        </is>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Astra G 1998-2009</t>
+          <t>V01589</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>V01085W</t>
-        </is>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Ford Transit Connect след 2018 година</t>
+          <t>V01600</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>V01574B</t>
+          <t>V01601</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>V01796A</t>
-        </is>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>Кутия Rati Frunk за преден багажник на Hyundai Kona Electric 2018-2023, Kia e-Niro 2018-2021, Kia e-Soul след 2020 година 24L, 52x39x19cm, черна</t>
+          <t>V01603</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>V01698</t>
+          <t>V01608</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>V01772</t>
-        </is>
-      </c>
-      <c r="B112" s="0" t="inlineStr">
-        <is>
-          <t>КОМПЛЕКТ СИВИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
+          <t>V01613</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>V01898C</t>
+          <t>V01618</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>ARMS-08</t>
-        </is>
-      </c>
-      <c r="B114" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Spring след 2021 година</t>
+          <t>V01620</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>ARMS-16</t>
-        </is>
-      </c>
-      <c r="B115" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus 2015-2017</t>
+          <t>V01622</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>ARMS-07</t>
-        </is>
-      </c>
-      <c r="B116" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Dacia Duster след 2018 година</t>
+          <t>V01625</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>ARMS-15</t>
-        </is>
-      </c>
-      <c r="B117" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus 2011-2014</t>
+          <t>V01633</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>ARMS-23</t>
-        </is>
-      </c>
-      <c r="B118" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa D 2006-2014</t>
+          <t>V01634</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>V01589</t>
+          <t>V01635</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>V01622</t>
+          <t>V01640</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>V01657A</t>
+          <t>V01647</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>V01770</t>
-        </is>
-      </c>
-      <c r="B122" s="0" t="inlineStr">
-        <is>
-          <t>КОМПЛЕКТ ЧЕРВЕНИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
+          <t>V01651</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>V01796C</t>
+          <t>V01657A</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>V01676</t>
+          <t>V01659</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>V01764</t>
-        </is>
-      </c>
-      <c r="B125" s="0" t="inlineStr">
-        <is>
-          <t>Комплект протектори Rati за врати 4 броя, черни</t>
+          <t>V01667</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>V01732</t>
+          <t>V01669</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>ARMS-24</t>
-        </is>
-      </c>
-      <c r="B127" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa E 2014-2019</t>
+          <t>V01670</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>ARMS-32</t>
-        </is>
-      </c>
-      <c r="B128" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Caddy след 2020 година</t>
+          <t>V01676</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>ARMS-09</t>
-        </is>
-      </c>
-      <c r="B129" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500 2008-2015</t>
+          <t>V01683</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>ARMS-17</t>
-        </is>
-      </c>
-      <c r="B130" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа, USB и AUX за Ford Focus след 2018 година</t>
+          <t>V01698</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>ARMS-25</t>
-        </is>
-      </c>
-      <c r="B131" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Corsa F след 2020 година</t>
+          <t>V01732</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>ARMS-31</t>
-        </is>
-      </c>
-      <c r="B132" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Caddy 2004-2020</t>
+          <t>V01737</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>ARMS-33</t>
-        </is>
-      </c>
-      <c r="B133" s="0" t="inlineStr">
-        <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Golf 5 2003-2010</t>
+          <t>V01743</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>ARM3-32</t>
+          <t>V01762</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster 3 с черна еко кожа за Volkswagen Caddy след 2020 година</t>
+          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива със синьо сива дръжка</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>ARMS-02</t>
+          <t>V01763</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Citroen C3 след 2017 година</t>
+          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива с червено сива дръжка</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>V00604</t>
+          <t>V01764</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Polo 2001-2009</t>
+          <t>Комплект протектори Rati за врати 4 броя, черни</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>V00867</t>
+          <t>V01768</t>
         </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Peugeot 206 1998-2012</t>
+          <t>ЧАНТА RATI ЗА СЕДАЛКА НА АВТОМОБИЛ 38X48CM</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>V01566</t>
+          <t>V01770</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>КОМПЛЕКТ ЧЕРВЕНИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>V01580</t>
+          <t>V01771</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>КОМПЛЕКТ ЗЕЛЕНИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>V01608</t>
+          <t>V01772</t>
+        </is>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>КОМПЛЕКТ СИВИ СТОПЕРИ RATI NOOK ЗА БАГАЖНИК - 2 БРОЯ</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>V01635</t>
+          <t>V01782A</t>
+        </is>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Fiat Ducato, Peugeot Boxer, Citroen Jumper след 2006 година, Opel Movano след 2021 година, Ram Promaster след 2014 година за моделите с фабричен подлакътник</t>
         </is>
       </c>
     </row>
@@ -1845,67 +1850,115 @@
     <row outlineLevel="0" r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>V01670</t>
+          <t>V01790A</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Volkswagen T5 2003-2016, T6 2016-2022, T7 след 2022 година, ID.Buzz след 2022 година за моделите с фабричен подлакътник</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>V01763</t>
+          <t>V01792</t>
         </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>Кошница Rati с подложка, обем 21L, товаримост 12kg, тъмно сива с червено сива дръжка</t>
+          <t>Кутия Rati Frunk за преден багажник на Fiat 500e след 2020 година 13L, 44x31x6/13cm, черна</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>ARMS-10</t>
+          <t>V01796A</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Fiat 500 след 2016 година, без електрическата версия</t>
+          <t>Кутия Rati Frunk за преден багажник на Hyundai Kona Electric 2018-2023, Kia e-Niro 2018-2021, Kia e-Soul след 2020 година 24L, 52x39x19cm, черна</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>ARMS-18</t>
+          <t>V01796B</t>
         </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Honda Jazz 2008-2015</t>
+          <t>Кутия Rati Frunk за преден багажник на Kia E-Niro 2018-2023, 24L, 49x35x12/15 cm, черна</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>ARMS-26</t>
+          <t>V01796C</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Opel Meriva 2010-2017 без подвижда релса в средната конзола</t>
+          <t>Кутия Rati Frunk за преден багажник на Kia E-Soul след 2020 година, 24L, 49x35x12/15 cm, черна</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>ARMS-34</t>
+          <t>V01802A</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>Подлакътник Rati модел Armster S с черна еко кожа за Volkswagen Golf 7 2012-2019</t>
+          <t>Подлакътник Rati модел Armster ОЕ1 с черна еко кожа за Ford Transit след 2013 година за модела с фабричен подлакътник</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>V01884A</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>Кутия Rati Frunk за преден багажник на MG 4 след 2023 година, 12L, 49x34x3/10 cm, черна</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>V01898C</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>V01945B</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>Кутия Rati Frunk за преден багажник на Ford Capri след 2024 година, 10L, 49x34x1/8 cm, черна</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t>V01946C</t>
+        </is>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t>Кутия Rati Frunk за преден багажник на Nissan Micra след 2025 година, 13L, черна</t>
         </is>
       </c>
     </row>
